--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20211.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="46">
   <si>
     <t>Mat</t>
   </si>
@@ -79,16 +79,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>MARCIAL</t>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
   </si>
   <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>ROSAS</t>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MONSALVO</t>
   </si>
   <si>
     <t>ARIAS</t>
@@ -100,37 +106,46 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>QUINTERO</t>
   </si>
   <si>
     <t>BARRAGAN</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>DIAZ</t>
   </si>
   <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>IVAN DE JESUS</t>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>SUSANA</t>
+  </si>
+  <si>
+    <t>LEONARDO GAEL</t>
   </si>
   <si>
     <t>CONSTANZA XIMENA</t>
   </si>
   <si>
-    <t>MONSERRAT</t>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>ANGEL GERARDO</t>
   </si>
   <si>
     <t>ANALI</t>
@@ -566,16 +581,16 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>52.38</v>
+        <v>57.14</v>
       </c>
       <c r="H3">
         <v>9.300000000000001</v>
@@ -683,16 +698,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>41.94</v>
+      </c>
+      <c r="H2">
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -706,16 +724,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>42.86</v>
+      </c>
+      <c r="H3">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -729,16 +750,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>65.70999999999999</v>
+      </c>
+      <c r="H4">
+        <v>8.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -752,16 +776,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>48.48</v>
+      </c>
+      <c r="H5">
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -826,7 +853,7 @@
         <v>64.52</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -840,16 +867,16 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>52.38</v>
+        <v>57.14</v>
       </c>
       <c r="H3">
         <v>9.300000000000001</v>
@@ -878,7 +905,7 @@
         <v>74.29000000000001</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -904,7 +931,7 @@
         <v>60.61</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -914,7 +941,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -946,163 +973,209 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920314</v>
+        <v>20330051920190</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920136</v>
+        <v>20330051920213</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920151</v>
+        <v>20330051920264</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920407</v>
+        <v>20330051920151</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920191</v>
+        <v>19330051920251</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920202</v>
+        <v>19330051920400</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920270</v>
+        <v>20330051920191</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920202</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920270</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
         <v>11</v>
       </c>
-      <c r="G8">
-        <v>6</v>
+      <c r="G10">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20211.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="49">
   <si>
     <t>Mat</t>
   </si>
@@ -88,6 +88,9 @@
     <t>CLEMENTE</t>
   </si>
   <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
@@ -115,6 +118,9 @@
     <t>GARNICA</t>
   </si>
   <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -137,6 +143,9 @@
   </si>
   <si>
     <t>LEONARDO GAEL</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>CONSTANZA XIMENA</t>
@@ -941,7 +950,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -979,10 +988,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1002,10 +1011,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1025,10 +1034,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1042,16 +1051,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920151</v>
+        <v>20330051920387</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1060,27 +1069,27 @@
         <v>12</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920251</v>
+        <v>20330051920151</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -1088,16 +1097,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920400</v>
+        <v>19330051920251</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1111,39 +1120,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920191</v>
+        <v>19330051920400</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920202</v>
+        <v>20330051920191</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1157,24 +1166,47 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920270</v>
+        <v>20330051920202</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920270</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
         <v>11</v>
       </c>
-      <c r="G10">
+      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20211.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20211.xlsx
@@ -1046,7 +1046,7 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1092,7 +1092,7 @@
         <v>12</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20211.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="80">
   <si>
     <t>Mat</t>
   </si>
@@ -79,91 +79,184 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CEREZO</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>BENITEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>ASCENCION</t>
   </si>
   <si>
-    <t>ROMERO</t>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>CLEMENTE</t>
   </si>
   <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>ZUNO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>ROSAS</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MONSALVO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>OLIVERA</t>
+  </si>
+  <si>
+    <t>DAMIEN</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>ZACARIAS</t>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>GARNICA</t>
   </si>
   <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
     <t>SALAZAR</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>QUINTERO</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
+    <t>DULCE FERNANDA</t>
+  </si>
+  <si>
+    <t>SILVIA ANGELICA</t>
+  </si>
+  <si>
+    <t>KITZIA YAMILET</t>
+  </si>
+  <si>
+    <t>SHADAI COSTANTIN</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>DIEGO ABDEL JARIN</t>
   </si>
   <si>
     <t>REYNA ARISBETH</t>
   </si>
   <si>
-    <t>SUSANA</t>
+    <t>CLARET YAZMIN</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>AMADA ARELY</t>
+  </si>
+  <si>
+    <t>JOSSELIN ANDREA</t>
   </si>
   <si>
     <t>LEONARDO GAEL</t>
   </si>
   <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>URIEL ALFREDO</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
     <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>CONSTANZA XIMENA</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>ANGEL GERARDO</t>
-  </si>
-  <si>
-    <t>ANALI</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>ELIAS ALONSO</t>
   </si>
 </sst>
 </file>
@@ -564,19 +657,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>64.52</v>
+        <v>74.19</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -590,19 +683,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -616,19 +709,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>74.29000000000001</v>
+        <v>82.86</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -642,19 +735,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>60.61</v>
+        <v>63.64</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -707,19 +800,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>41.94</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H2">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -733,19 +826,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>42.86</v>
+        <v>66.67</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -759,19 +852,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>65.70999999999999</v>
+        <v>82.86</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -785,19 +878,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G5">
-        <v>48.48</v>
+        <v>60.61</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -850,10 +943,10 @@
         <v>31</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>11</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
       </c>
       <c r="F2">
         <v>20</v>
@@ -862,7 +955,7 @@
         <v>64.52</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -876,19 +969,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -902,19 +995,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>74.29000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -928,10 +1021,10 @@
         <v>33</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>13</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
       </c>
       <c r="F5">
         <v>20</v>
@@ -940,7 +1033,7 @@
         <v>60.61</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -950,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -982,16 +1075,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920190</v>
+        <v>20330051920193</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1005,16 +1098,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920213</v>
+        <v>20330051920392</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1028,22 +1121,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920264</v>
+        <v>20330051920194</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1051,22 +1144,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920387</v>
+        <v>20330051920203</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1074,22 +1167,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920151</v>
+        <v>20330051920204</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1097,45 +1190,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920251</v>
+        <v>20330051920207</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920400</v>
+        <v>20330051920261</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1143,62 +1236,62 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920191</v>
+        <v>20330051920267</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920202</v>
+        <v>20330051920278</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920270</v>
+        <v>20330051920281</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1207,6 +1300,305 @@
         <v>11</v>
       </c>
       <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920126</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330051920251</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19330051920259</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920190</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920205</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920214</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>20330051920215</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>19330051920177</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920264</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20330051920282</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>19330051920425</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920122</v>
+      </c>
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>20330051920387</v>
+      </c>
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20211.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20211.xlsx
@@ -106,6 +106,9 @@
     <t>TELLEZ</t>
   </si>
   <si>
+    <t>ZUNO</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -130,9 +133,6 @@
     <t>TINOCO</t>
   </si>
   <si>
-    <t>ZUNO</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -223,6 +223,9 @@
     <t>MARISOL</t>
   </si>
   <si>
+    <t>URIEL ALFREDO</t>
+  </si>
+  <si>
     <t>ESMERALDA</t>
   </si>
   <si>
@@ -248,9 +251,6 @@
   </si>
   <si>
     <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>URIEL ALFREDO</t>
   </si>
   <si>
     <t>JAVIER</t>
@@ -1127,7 +1127,7 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
         <v>60</v>
@@ -1305,13 +1305,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920126</v>
+        <v>19330051920425</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
         <v>68</v>
@@ -1320,7 +1320,7 @@
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1328,22 +1328,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920251</v>
+        <v>20330051920126</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1351,16 +1351,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920259</v>
+        <v>19330051920251</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1374,36 +1374,36 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920190</v>
+        <v>19330051920259</v>
       </c>
       <c r="B15" t="s">
         <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
         <v>70</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920205</v>
+        <v>20330051920190</v>
       </c>
       <c r="B16" t="s">
         <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
         <v>71</v>
@@ -1420,13 +1420,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920214</v>
+        <v>20330051920205</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
         <v>72</v>
@@ -1443,13 +1443,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920215</v>
+        <v>20330051920214</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
         <v>73</v>
@@ -1466,13 +1466,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920177</v>
+        <v>20330051920215</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D19" t="s">
         <v>74</v>
@@ -1489,13 +1489,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920264</v>
+        <v>19330051920177</v>
       </c>
       <c r="B20" t="s">
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s">
         <v>75</v>
@@ -1504,7 +1504,7 @@
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1512,13 +1512,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920282</v>
+        <v>20330051920264</v>
       </c>
       <c r="B21" t="s">
         <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
         <v>76</v>
@@ -1535,13 +1535,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051920425</v>
+        <v>20330051920282</v>
       </c>
       <c r="B22" t="s">
         <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
         <v>77</v>
